--- a/tool/src/main/resources/xml/TableModel.xlsx
+++ b/tool/src/main/resources/xml/TableModel.xlsx
@@ -1,90 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226" filterPrivacy="true"/>
   <sheets>
     <sheet name="room" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型(1麻将2斗地主)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seatNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>座位数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cardNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牌数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>exCardNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外牌数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -109,26 +65,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -170,7 +118,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -205,7 +153,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -272,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -407,71 +351,273 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:U4"/>
   <cols>
-    <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="18" width="18.83203125" customWidth="1"/>
+    <col min="19" max="19" width="18.83203125" customWidth="1"/>
+    <col min="20" max="20" width="18.83203125" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>seatNum</v>
+      </c>
+      <c r="D1" t="str">
+        <v>cardNum</v>
+      </c>
+      <c r="E1" t="str">
+        <v>exCardNum</v>
+      </c>
+      <c r="F1" t="str">
+        <v>baseScore</v>
+      </c>
+      <c r="G1" t="str">
+        <v>maxFan</v>
+      </c>
+      <c r="H1" t="str">
+        <v>allowChi</v>
+      </c>
+      <c r="I1" t="str">
+        <v>allowDianPao</v>
+      </c>
+      <c r="J1" t="str">
+        <v>allowPeng</v>
+      </c>
+      <c r="K1" t="str">
+        <v>allowGang</v>
+      </c>
+      <c r="L1" t="str">
+        <v>allowHu</v>
+      </c>
+      <c r="M1" t="str">
+        <v>allowSevenPairs</v>
+      </c>
+      <c r="N1" t="str">
+        <v>gameSubType</v>
+      </c>
+      <c r="O1" t="str">
+        <v>gangScore</v>
+      </c>
+      <c r="P1" t="str">
+        <v>allowGangMing</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>allowGangAn</v>
+      </c>
+      <c r="R1" t="str">
+        <v>allowGangBu</v>
+      </c>
+      <c r="S1" t="str">
+        <v>totalRounds</v>
+      </c>
+      <c r="T1" t="str">
+        <v>autoNextRound</v>
+      </c>
+      <c r="U1" t="str">
+        <v>autoPlay</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>int</v>
+      </c>
+      <c r="B2" t="str">
+        <v>int</v>
+      </c>
+      <c r="C2" t="str">
+        <v>int</v>
+      </c>
+      <c r="D2" t="str">
+        <v>int</v>
+      </c>
+      <c r="E2" t="str">
+        <v>int</v>
+      </c>
+      <c r="F2" t="str">
+        <v>int</v>
+      </c>
+      <c r="G2" t="str">
+        <v>int</v>
+      </c>
+      <c r="H2" t="str">
+        <v>int</v>
+      </c>
+      <c r="I2" t="str">
+        <v>int</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="str">
+        <v>int</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>int</v>
+      </c>
+      <c r="R2" t="str">
+        <v>int</v>
+      </c>
+      <c r="S2" t="str">
+        <v>int</v>
+      </c>
+      <c r="T2" t="str">
+        <v>int</v>
+      </c>
+      <c r="U2" t="str">
+        <v>int</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>主键</v>
+      </c>
+      <c r="B3" t="str">
+        <v>类型(1麻将2斗地主)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>座位数量</v>
+      </c>
+      <c r="D3" t="str">
+        <v>牌数量</v>
+      </c>
+      <c r="E3" t="str">
+        <v>额外牌数量</v>
+      </c>
+      <c r="F3" t="str">
+        <v>底分</v>
+      </c>
+      <c r="G3" t="str">
+        <v>番数上限(麻将用)</v>
+      </c>
+      <c r="H3" t="str">
+        <v>允许吃(麻将用 0关1开)</v>
+      </c>
+      <c r="I3" t="str">
+        <v>允许点炮(麻将用 0关1开)</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" t="str">
+        <v>allowGangMing</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>allowGangAn</v>
+      </c>
+      <c r="R3" t="str">
+        <v>allowGangBu</v>
+      </c>
+      <c r="S3" t="str">
+        <v>totalRounds</v>
+      </c>
+      <c r="T3" t="str">
+        <v>autoNextRound</v>
+      </c>
+      <c r="U3" t="str">
+        <v>超时自动(0关1开)</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -487,10 +633,58 @@
       <c r="E4">
         <v>3</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>16</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:U4"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/tool/src/main/resources/xml/TableModel.xlsx
+++ b/tool/src/main/resources/xml/TableModel.xlsx
@@ -1,46 +1,135 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226" filterPrivacy="true"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C94D12-1C99-411F-9B80-9045E23AE194}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="room" sheetId="1" r:id="rId1"/>
+    <sheet name="TableModel" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>seatNum</t>
+  </si>
+  <si>
+    <t>cardNum</t>
+  </si>
+  <si>
+    <t>exCardNum</t>
+  </si>
+  <si>
+    <t>baseScore</t>
+  </si>
+  <si>
+    <t>maxFan</t>
+  </si>
+  <si>
+    <t>allowChi</t>
+  </si>
+  <si>
+    <t>allowDianPao</t>
+  </si>
+  <si>
+    <t>allowPeng</t>
+  </si>
+  <si>
+    <t>allowGang</t>
+  </si>
+  <si>
+    <t>allowHu</t>
+  </si>
+  <si>
+    <t>allowSevenPairs</t>
+  </si>
+  <si>
+    <t>gameSubType</t>
+  </si>
+  <si>
+    <t>gangScore</t>
+  </si>
+  <si>
+    <t>allowGangMing</t>
+  </si>
+  <si>
+    <t>allowGangAn</t>
+  </si>
+  <si>
+    <t>allowGangBu</t>
+  </si>
+  <si>
+    <t>totalRounds</t>
+  </si>
+  <si>
+    <t>autoNextRound</t>
+  </si>
+  <si>
+    <t>autoPlay</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>主键</t>
+  </si>
+  <si>
+    <t>类型(1麻将2斗地主)</t>
+  </si>
+  <si>
+    <t>座位数量</t>
+  </si>
+  <si>
+    <t>牌数量</t>
+  </si>
+  <si>
+    <t>额外牌数量</t>
+  </si>
+  <si>
+    <t>底分</t>
+  </si>
+  <si>
+    <t>番数上限(麻将用)</t>
+  </si>
+  <si>
+    <t>允许吃(麻将用 0关1开)</t>
+  </si>
+  <si>
+    <t>允许点炮(麻将用 0关1开)</t>
+  </si>
+  <si>
+    <t>超时自动(0关1开)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -68,15 +157,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -118,7 +215,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -151,9 +248,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -186,6 +300,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +351,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,234 +486,176 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="18.83203125" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" customWidth="1"/>
-    <col min="16" max="16" width="18.83203125" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" customWidth="1"/>
-    <col min="18" max="18" width="18.83203125" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" customWidth="1"/>
-    <col min="20" max="20" width="18.83203125" customWidth="1"/>
-    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="1" max="21" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>seatNum</v>
-      </c>
-      <c r="D1" t="str">
-        <v>cardNum</v>
-      </c>
-      <c r="E1" t="str">
-        <v>exCardNum</v>
-      </c>
-      <c r="F1" t="str">
-        <v>baseScore</v>
-      </c>
-      <c r="G1" t="str">
-        <v>maxFan</v>
-      </c>
-      <c r="H1" t="str">
-        <v>allowChi</v>
-      </c>
-      <c r="I1" t="str">
-        <v>allowDianPao</v>
-      </c>
-      <c r="J1" t="str">
-        <v>allowPeng</v>
-      </c>
-      <c r="K1" t="str">
-        <v>allowGang</v>
-      </c>
-      <c r="L1" t="str">
-        <v>allowHu</v>
-      </c>
-      <c r="M1" t="str">
-        <v>allowSevenPairs</v>
-      </c>
-      <c r="N1" t="str">
-        <v>gameSubType</v>
-      </c>
-      <c r="O1" t="str">
-        <v>gangScore</v>
-      </c>
-      <c r="P1" t="str">
-        <v>allowGangMing</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>allowGangAn</v>
-      </c>
-      <c r="R1" t="str">
-        <v>allowGangBu</v>
-      </c>
-      <c r="S1" t="str">
-        <v>totalRounds</v>
-      </c>
-      <c r="T1" t="str">
-        <v>autoNextRound</v>
-      </c>
-      <c r="U1" t="str">
-        <v>autoPlay</v>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>int</v>
-      </c>
-      <c r="B2" t="str">
-        <v>int</v>
-      </c>
-      <c r="C2" t="str">
-        <v>int</v>
-      </c>
-      <c r="D2" t="str">
-        <v>int</v>
-      </c>
-      <c r="E2" t="str">
-        <v>int</v>
-      </c>
-      <c r="F2" t="str">
-        <v>int</v>
-      </c>
-      <c r="G2" t="str">
-        <v>int</v>
-      </c>
-      <c r="H2" t="str">
-        <v>int</v>
-      </c>
-      <c r="I2" t="str">
-        <v>int</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" t="str">
-        <v>int</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>int</v>
-      </c>
-      <c r="R2" t="str">
-        <v>int</v>
-      </c>
-      <c r="S2" t="str">
-        <v>int</v>
-      </c>
-      <c r="T2" t="str">
-        <v>int</v>
-      </c>
-      <c r="U2" t="str">
-        <v>int</v>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>主键</v>
-      </c>
-      <c r="B3" t="str">
-        <v>类型(1麻将2斗地主)</v>
-      </c>
-      <c r="C3" t="str">
-        <v>座位数量</v>
-      </c>
-      <c r="D3" t="str">
-        <v>牌数量</v>
-      </c>
-      <c r="E3" t="str">
-        <v>额外牌数量</v>
-      </c>
-      <c r="F3" t="str">
-        <v>底分</v>
-      </c>
-      <c r="G3" t="str">
-        <v>番数上限(麻将用)</v>
-      </c>
-      <c r="H3" t="str">
-        <v>允许吃(麻将用 0关1开)</v>
-      </c>
-      <c r="I3" t="str">
-        <v>允许点炮(麻将用 0关1开)</v>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -598,26 +675,26 @@
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3" t="str">
-        <v>allowGangMing</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>allowGangAn</v>
-      </c>
-      <c r="R3" t="str">
-        <v>allowGangBu</v>
-      </c>
-      <c r="S3" t="str">
-        <v>totalRounds</v>
-      </c>
-      <c r="T3" t="str">
-        <v>autoNextRound</v>
-      </c>
-      <c r="U3" t="str">
-        <v>超时自动(0关1开)</v>
+      <c r="P3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>1</v>
       </c>
@@ -683,8 +760,11 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U4"/>
+    <ignoredError sqref="A1:U1 A3:U4 A2:I2 P2:U2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>